--- a/instrument_dict_2026-02-06.xlsx
+++ b/instrument_dict_2026-02-06.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1916776</v>
+        <v>1988902</v>
       </c>
     </row>
     <row r="4">
@@ -482,7 +482,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1988902</v>
+        <v>1916778</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1916778</v>
+        <v>1988904</v>
       </c>
     </row>
     <row r="6">
@@ -522,7 +522,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1988904</v>
+        <v>1916780</v>
       </c>
     </row>
     <row r="7">
@@ -542,7 +542,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1916780</v>
+        <v>1988906</v>
       </c>
     </row>
     <row r="8">
@@ -562,7 +562,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1988906</v>
+        <v>1916782</v>
       </c>
     </row>
     <row r="9">
@@ -582,7 +582,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1916782</v>
+        <v>1988908</v>
       </c>
     </row>
     <row r="10">
@@ -602,7 +602,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1988908</v>
+        <v>1916784</v>
       </c>
     </row>
     <row r="11">
@@ -622,7 +622,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1916784</v>
+        <v>1988910</v>
       </c>
     </row>
     <row r="12">
@@ -642,7 +642,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1988910</v>
+        <v>1916786</v>
       </c>
     </row>
     <row r="13">
@@ -662,7 +662,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1916786</v>
+        <v>1988912</v>
       </c>
     </row>
     <row r="14">
@@ -682,7 +682,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1988912</v>
+        <v>1916788</v>
       </c>
     </row>
     <row r="15">
@@ -702,7 +702,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1916788</v>
+        <v>1988914</v>
       </c>
     </row>
     <row r="16">
@@ -722,7 +722,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1988914</v>
+        <v>1916790</v>
       </c>
     </row>
     <row r="17">
@@ -742,7 +742,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1916790</v>
+        <v>1988916</v>
       </c>
     </row>
     <row r="18">
@@ -762,7 +762,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1988916</v>
+        <v>1916792</v>
       </c>
     </row>
     <row r="19">
@@ -782,7 +782,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1916792</v>
+        <v>1988918</v>
       </c>
     </row>
     <row r="20">
@@ -802,7 +802,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1988918</v>
+        <v>1916794</v>
       </c>
     </row>
     <row r="21">
@@ -822,7 +822,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1916794</v>
+        <v>1988920</v>
       </c>
     </row>
     <row r="22">
@@ -842,7 +842,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1988920</v>
+        <v>1916796</v>
       </c>
     </row>
     <row r="23">
@@ -862,7 +862,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1916796</v>
+        <v>1988922</v>
       </c>
     </row>
     <row r="24">
@@ -882,7 +882,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1988922</v>
+        <v>1916798</v>
       </c>
     </row>
     <row r="25">
@@ -902,7 +902,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1916798</v>
+        <v>1988924</v>
       </c>
     </row>
     <row r="26">
@@ -922,7 +922,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1988924</v>
+        <v>1916800</v>
       </c>
     </row>
     <row r="27">
@@ -942,7 +942,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1916800</v>
+        <v>1988926</v>
       </c>
     </row>
     <row r="28">
@@ -962,7 +962,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1916777</v>
+        <v>1988903</v>
       </c>
     </row>
     <row r="29">
@@ -982,7 +982,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1988903</v>
+        <v>1916779</v>
       </c>
     </row>
     <row r="30">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1916779</v>
+        <v>1988905</v>
       </c>
     </row>
     <row r="31">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1988905</v>
+        <v>1916781</v>
       </c>
     </row>
     <row r="32">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1916781</v>
+        <v>1988907</v>
       </c>
     </row>
     <row r="33">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1988907</v>
+        <v>1916783</v>
       </c>
     </row>
     <row r="34">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1916783</v>
+        <v>1988909</v>
       </c>
     </row>
     <row r="35">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1988909</v>
+        <v>1916785</v>
       </c>
     </row>
     <row r="36">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1916785</v>
+        <v>1988911</v>
       </c>
     </row>
     <row r="37">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1988911</v>
+        <v>1916787</v>
       </c>
     </row>
     <row r="38">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1916787</v>
+        <v>1988913</v>
       </c>
     </row>
     <row r="39">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1988913</v>
+        <v>1916789</v>
       </c>
     </row>
     <row r="40">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1916789</v>
+        <v>1988915</v>
       </c>
     </row>
     <row r="41">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1988915</v>
+        <v>1916791</v>
       </c>
     </row>
     <row r="42">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1916791</v>
+        <v>1988917</v>
       </c>
     </row>
     <row r="43">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1988917</v>
+        <v>1916793</v>
       </c>
     </row>
     <row r="44">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1916793</v>
+        <v>1988919</v>
       </c>
     </row>
     <row r="45">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1988919</v>
+        <v>1916795</v>
       </c>
     </row>
     <row r="46">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1916795</v>
+        <v>1988921</v>
       </c>
     </row>
     <row r="47">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1988921</v>
+        <v>1916797</v>
       </c>
     </row>
     <row r="48">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1916797</v>
+        <v>1988923</v>
       </c>
     </row>
     <row r="49">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1988923</v>
+        <v>1916799</v>
       </c>
     </row>
     <row r="50">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1916799</v>
+        <v>1988925</v>
       </c>
     </row>
     <row r="51">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1988925</v>
+        <v>1916801</v>
       </c>
     </row>
     <row r="52">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1916801</v>
+        <v>1988927</v>
       </c>
     </row>
     <row r="53">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>850</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1895202</v>
+        <v>1959535</v>
       </c>
     </row>
     <row r="114">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>860</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1959535</v>
+        <v>1959537</v>
       </c>
     </row>
     <row r="115">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>870</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1959537</v>
+        <v>1959539</v>
       </c>
     </row>
     <row r="116">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>880</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1959539</v>
+        <v>1895204</v>
       </c>
     </row>
     <row r="117">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>890</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1895204</v>
+        <v>1959541</v>
       </c>
     </row>
     <row r="118">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>900</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1959541</v>
+        <v>1959543</v>
       </c>
     </row>
     <row r="119">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>910</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1959543</v>
+        <v>1959545</v>
       </c>
     </row>
     <row r="120">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>920</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1959545</v>
+        <v>1895206</v>
       </c>
     </row>
     <row r="121">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>930</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1895206</v>
+        <v>1959547</v>
       </c>
     </row>
     <row r="122">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>940</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1959547</v>
+        <v>1959549</v>
       </c>
     </row>
     <row r="123">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1959549</v>
+        <v>1959551</v>
       </c>
     </row>
     <row r="124">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>960</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1959551</v>
+        <v>1895208</v>
       </c>
     </row>
     <row r="125">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>970</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1895208</v>
+        <v>1959553</v>
       </c>
     </row>
     <row r="126">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>980</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1959553</v>
+        <v>1959555</v>
       </c>
     </row>
     <row r="127">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1959555</v>
+        <v>1959557</v>
       </c>
     </row>
     <row r="128">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1959557</v>
+        <v>1895210</v>
       </c>
     </row>
     <row r="129">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1895210</v>
+        <v>1959559</v>
       </c>
     </row>
     <row r="130">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1959559</v>
+        <v>1959561</v>
       </c>
     </row>
     <row r="131">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1959561</v>
+        <v>1959563</v>
       </c>
     </row>
     <row r="132">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1959563</v>
+        <v>1895212</v>
       </c>
     </row>
     <row r="133">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1895212</v>
+        <v>1959565</v>
       </c>
     </row>
     <row r="134">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1959565</v>
+        <v>1959567</v>
       </c>
     </row>
     <row r="135">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1959567</v>
+        <v>1959569</v>
       </c>
     </row>
     <row r="136">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1959569</v>
+        <v>1895214</v>
       </c>
     </row>
     <row r="137">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1895214</v>
+        <v>1959571</v>
       </c>
     </row>
     <row r="138">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>850</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1895203</v>
+        <v>1959536</v>
       </c>
     </row>
     <row r="139">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>860</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1959536</v>
+        <v>1959538</v>
       </c>
     </row>
     <row r="140">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>870</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1959538</v>
+        <v>1959540</v>
       </c>
     </row>
     <row r="141">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>880</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1959540</v>
+        <v>1895205</v>
       </c>
     </row>
     <row r="142">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>890</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1895205</v>
+        <v>1959542</v>
       </c>
     </row>
     <row r="143">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>900</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1959542</v>
+        <v>1959544</v>
       </c>
     </row>
     <row r="144">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>910</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1959544</v>
+        <v>1959546</v>
       </c>
     </row>
     <row r="145">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>920</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1959546</v>
+        <v>1895207</v>
       </c>
     </row>
     <row r="146">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>930</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1895207</v>
+        <v>1959548</v>
       </c>
     </row>
     <row r="147">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>940</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1959548</v>
+        <v>1959550</v>
       </c>
     </row>
     <row r="148">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1959550</v>
+        <v>1959552</v>
       </c>
     </row>
     <row r="149">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>960</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1959552</v>
+        <v>1895209</v>
       </c>
     </row>
     <row r="150">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>970</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1895209</v>
+        <v>1959554</v>
       </c>
     </row>
     <row r="151">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>980</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1959554</v>
+        <v>1959556</v>
       </c>
     </row>
     <row r="152">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1959556</v>
+        <v>1959558</v>
       </c>
     </row>
     <row r="153">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1959558</v>
+        <v>1895211</v>
       </c>
     </row>
     <row r="154">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1895211</v>
+        <v>1959560</v>
       </c>
     </row>
     <row r="155">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1959560</v>
+        <v>1959562</v>
       </c>
     </row>
     <row r="156">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1959562</v>
+        <v>1959564</v>
       </c>
     </row>
     <row r="157">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1959564</v>
+        <v>1895213</v>
       </c>
     </row>
     <row r="158">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1895213</v>
+        <v>1959566</v>
       </c>
     </row>
     <row r="159">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1959566</v>
+        <v>1959568</v>
       </c>
     </row>
     <row r="160">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1959568</v>
+        <v>1959570</v>
       </c>
     </row>
     <row r="161">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1959570</v>
+        <v>1895215</v>
       </c>
     </row>
     <row r="162">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1895215</v>
+        <v>1959572</v>
       </c>
     </row>
   </sheetData>
